--- a/data/2.full_abstracting/26_06_full_decisions.xlsx
+++ b/data/2.full_abstracting/26_06_full_decisions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/2.full_abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2672" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF0AD28-2F6C-4E24-B26B-37D6480C7C8F}"/>
+  <xr:revisionPtr revIDLastSave="2677" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CEF0ED1-217F-4807-AC7F-311E8DD1359B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4731,7 +4731,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4741,12 +4741,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4764,7 +4758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4775,10 +4769,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="17" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="17" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -5449,178 +5439,178 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="10" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8">
+    <row r="7" spans="1:31" s="5" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
         <v>46174</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="5" t="s">
         <v>1542</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="6" t="s">
         <v>1496</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="5" t="s">
         <v>1551</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="5" t="s">
         <v>1526</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="5" t="s">
         <v>1503</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="5" t="s">
         <v>1511</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="5" t="s">
         <v>1534</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="5">
         <v>2026</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="5" t="s">
         <v>1455</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>1424</v>
-      </c>
-      <c r="N7" s="10" t="s">
+      <c r="M7" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>1548</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>1439</v>
-      </c>
-      <c r="P7" s="11" t="s">
+      <c r="O7" s="5" t="s">
+        <v>1486</v>
+      </c>
+      <c r="P7" s="6" t="s">
         <v>1544</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="6" t="s">
         <v>1545</v>
       </c>
-      <c r="R7" s="10" t="s">
+      <c r="R7" s="5" t="s">
         <v>1161</v>
       </c>
-      <c r="S7" s="10" t="s">
+      <c r="S7" s="5" t="s">
         <v>1204</v>
       </c>
-      <c r="T7" s="10">
+      <c r="T7" s="5">
         <v>60.3</v>
       </c>
-      <c r="U7" s="10">
+      <c r="U7" s="5">
         <v>29.9</v>
       </c>
-      <c r="V7" s="10">
+      <c r="V7" s="5">
         <v>1103</v>
       </c>
-      <c r="W7" s="10" t="s">
+      <c r="W7" s="5" t="s">
         <v>1167</v>
       </c>
-      <c r="X7" s="10" t="s">
+      <c r="X7" s="5" t="s">
         <v>1452</v>
       </c>
-      <c r="Z7" s="10" t="s">
+      <c r="Z7" s="5" t="s">
         <v>1169</v>
       </c>
-      <c r="AA7" s="10" t="s">
+      <c r="AA7" s="5" t="s">
         <v>1162</v>
       </c>
-      <c r="AC7" s="10" t="s">
+      <c r="AC7" s="5" t="s">
         <v>1537</v>
       </c>
-      <c r="AD7" s="10" t="s">
+      <c r="AD7" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="10" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8">
+    <row r="8" spans="1:31" s="5" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
         <v>46174</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="5" t="s">
         <v>1139</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="5" t="s">
         <v>1543</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="6" t="s">
         <v>1496</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="5" t="s">
         <v>1551</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="5" t="s">
         <v>1526</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="5" t="s">
         <v>1503</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="5" t="s">
         <v>1511</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="5" t="s">
         <v>1534</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="5">
         <v>2026</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="5" t="s">
         <v>1455</v>
       </c>
-      <c r="M8" s="10" t="s">
-        <v>1424</v>
-      </c>
-      <c r="N8" s="10" t="s">
+      <c r="M8" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>1547</v>
       </c>
-      <c r="O8" s="10" t="s">
-        <v>1439</v>
-      </c>
-      <c r="P8" s="11" t="s">
+      <c r="O8" s="5" t="s">
+        <v>1486</v>
+      </c>
+      <c r="P8" s="6" t="s">
         <v>1544</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="6" t="s">
         <v>1545</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="R8" s="5" t="s">
         <v>1162</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="S8" s="5" t="s">
         <v>1204</v>
       </c>
-      <c r="T8" s="10">
+      <c r="T8" s="5">
         <v>78.099999999999994</v>
       </c>
-      <c r="U8" s="10">
+      <c r="U8" s="5">
         <v>23.4</v>
       </c>
-      <c r="V8" s="10">
+      <c r="V8" s="5">
         <v>123</v>
       </c>
-      <c r="W8" s="10" t="s">
+      <c r="W8" s="5" t="s">
         <v>1167</v>
       </c>
-      <c r="X8" s="10" t="s">
+      <c r="X8" s="5" t="s">
         <v>1452</v>
       </c>
-      <c r="Z8" s="10" t="s">
+      <c r="Z8" s="5" t="s">
         <v>1169</v>
       </c>
-      <c r="AA8" s="10" t="s">
+      <c r="AA8" s="5" t="s">
         <v>1162</v>
       </c>
-      <c r="AB8" s="10" t="s">
+      <c r="AB8" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="AC8" s="10" t="s">
+      <c r="AC8" s="5" t="s">
         <v>1537</v>
       </c>
-      <c r="AD8" s="10" t="s">
+      <c r="AD8" s="5" t="s">
         <v>1546</v>
       </c>
     </row>
